--- a/MinMax/scripts/comparison/violations_comparison_table_118_5.xlsx
+++ b/MinMax/scripts/comparison/violations_comparison_table_118_5.xlsx
@@ -459,16 +459,16 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>0.0009107707301154733</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.0004289677017368376</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>0.009492707438766956</v>
+        <v>0.009489402174949646</v>
       </c>
       <c r="E2">
-        <v>0.01210443861782551</v>
+        <v>0.01210115291178226</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -476,10 +476,10 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>0.04059457778930664</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>0.04157733917236328</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <v>0.1031434535980225</v>
@@ -493,16 +493,16 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>0.0004677017568610609</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>0.0004857660387642682</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>0.005824837367981672</v>
+        <v>0.005825710948556662</v>
       </c>
       <c r="E4">
-        <v>0.005601311102509499</v>
+        <v>0.005602287128567696</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -510,16 +510,16 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>0.04352374747395515</v>
+        <v>-0</v>
       </c>
       <c r="C5">
-        <v>0.069937564432621</v>
+        <v>-0</v>
       </c>
       <c r="D5">
-        <v>0.07458364963531494</v>
+        <v>0.07481145858764648</v>
       </c>
       <c r="E5">
-        <v>0.09197986125946045</v>
+        <v>0.09221160411834717</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -567,7 +567,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>0.0006104636122472584</v>
+        <v>0.0006104635540395975</v>
       </c>
       <c r="E8">
         <v>0.002188535640016198</v>
@@ -629,10 +629,10 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>0.0001612678461242467</v>
+        <v>0.0001612846099305898</v>
       </c>
       <c r="C12">
-        <v>0.0001612850173842162</v>
+        <v>0.000161291376571171</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -646,10 +646,10 @@
         <v>16</v>
       </c>
       <c r="B13">
-        <v>0.01916271448135376</v>
+        <v>0.01916515827178955</v>
       </c>
       <c r="C13">
-        <v>0.01915949583053589</v>
+        <v>0.01916044950485229</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -663,10 +663,10 @@
         <v>17</v>
       </c>
       <c r="B14">
-        <v>0.1712246835231781</v>
+        <v>0.1712297201156616</v>
       </c>
       <c r="C14">
-        <v>0.1712333112955093</v>
+        <v>0.1712327748537064</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -680,10 +680,10 @@
         <v>18</v>
       </c>
       <c r="B15">
-        <v>8.22471809387207</v>
+        <v>8.22465705871582</v>
       </c>
       <c r="C15">
-        <v>8.225234985351562</v>
+        <v>8.224760055541992</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -697,16 +697,16 @@
         <v>19</v>
       </c>
       <c r="B16">
-        <v>5.167146492499307E-08</v>
+        <v>5.772968030640541E-08</v>
       </c>
       <c r="C16">
-        <v>5.8771103149435E-08</v>
+        <v>6.271233510710452E-08</v>
       </c>
       <c r="D16">
-        <v>2.085727575226815E-06</v>
+        <v>2.063303782051662E-06</v>
       </c>
       <c r="E16">
-        <v>2.049029826801058E-06</v>
+        <v>1.932833356477204E-06</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -714,16 +714,16 @@
         <v>20</v>
       </c>
       <c r="B17">
-        <v>1.414052590511971E-06</v>
+        <v>2.594122865991642E-06</v>
       </c>
       <c r="C17">
-        <v>2.935085482071499E-06</v>
+        <v>3.646981885426964E-06</v>
       </c>
       <c r="D17">
-        <v>4.387940487175952E-05</v>
+        <v>3.486841160338372E-05</v>
       </c>
       <c r="E17">
-        <v>3.578327571948287E-05</v>
+        <v>2.015158315771259E-05</v>
       </c>
     </row>
   </sheetData>
